--- a/data/trans_orig/P42B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P42B-Estudios-trans_orig.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -786,12 +786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -829,12 +829,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29696</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12232</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29696</t>
+          <t>29426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120491</t>
+          <t>120591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146542</t>
+          <t>147043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -922,12 +922,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120491</t>
+          <t>120591</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146542</t>
+          <t>147043</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1025,7 +1025,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>5166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>43628</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24229</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>45438</t>
+          <t>43628</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1113,12 +1113,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11725</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19289</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234342</t>
+          <t>235563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268073</t>
+          <t>268569</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234342</t>
+          <t>235563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268073</t>
+          <t>268569</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1507,12 +1507,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12224</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>30505</t>
+          <t>30030</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35669</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86490</t>
+          <t>87090</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105266</t>
+          <t>105009</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86490</t>
+          <t>87090</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>105266</t>
+          <t>105009</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18446</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -2401,12 +2401,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7790</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22494</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2479,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20494</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42829</t>
+          <t>41821</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>461134</t>
+          <t>464762</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>505826</t>
+          <t>508328</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>461134</t>
+          <t>464762</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>505826</t>
+          <t>508328</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,67%</t>
         </is>
       </c>
     </row>
@@ -2635,12 +2635,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21452</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45467</t>
+          <t>43352</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>75341</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>111201</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6435</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -3199,12 +3199,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11473</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>651726</t>
+          <t>650815</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>709629</t>
+          <t>709316</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>651726</t>
+          <t>650815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>709629</t>
+          <t>709316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,46%</t>
         </is>
       </c>
     </row>
@@ -3355,12 +3355,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39626</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39626</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3433,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>184646</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>238937</t>
+          <t>236946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>183827</t>
+          <t>184646</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>238937</t>
+          <t>236946</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15987</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36880</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3671,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4862</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3749,12 +3749,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24423</t>
+          <t>24426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>950833</t>
+          <t>954228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1020973</t>
+          <t>1022963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>950833</t>
+          <t>954228</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1020973</t>
+          <t>1022963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,94%</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91181</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>131435</t>
+          <t>130328</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3920,12 +3920,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>91181</t>
+          <t>90385</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>131435</t>
+          <t>130328</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -3983,12 +3983,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191629</t>
+          <t>191549</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>247818</t>
+          <t>244429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>191629</t>
+          <t>191549</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>247818</t>
+          <t>244429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4299,12 +4299,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4043</t>
+          <t>3997</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4349,12 +4349,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>286171</t>
+          <t>286177</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>323940</t>
+          <t>323253</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>286171</t>
+          <t>286177</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>323940</t>
+          <t>323253</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,51%</t>
         </is>
       </c>
     </row>
@@ -4455,12 +4455,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38624</t>
+          <t>37945</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>45652</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76930</t>
+          <t>76654</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46301</t>
+          <t>45652</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76930</t>
+          <t>76654</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -4693,12 +4693,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58447</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31483</t>
+          <t>30925</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58447</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34294</t>
+          <t>35198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -4806,12 +4806,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>15781</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34294</t>
+          <t>35198</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -4849,12 +4849,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -4864,12 +4864,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -4884,12 +4884,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>30977</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>58148</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -4899,12 +4899,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -4927,12 +4927,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1922417</t>
+          <t>1927276</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2022831</t>
+          <t>2024380</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1922417</t>
+          <t>1927276</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2022831</t>
+          <t>2024380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,96%</t>
         </is>
       </c>
     </row>
@@ -5005,12 +5005,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>139683</t>
+          <t>136429</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>191983</t>
+          <t>188996</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>139683</t>
+          <t>136429</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>191983</t>
+          <t>188996</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>450742</t>
+          <t>449932</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>531699</t>
+          <t>534225</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>450742</t>
+          <t>449932</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>531699</t>
+          <t>534225</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -5413,12 +5413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29967</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>11436</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29967</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8912</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5569,12 +5569,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31827</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58663</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5647,12 +5647,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>439214</t>
+          <t>439049</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>487790</t>
+          <t>488255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5662,12 +5662,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>439214</t>
+          <t>439049</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>487790</t>
+          <t>488255</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -5725,12 +5725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39902</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>39902</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113339</t>
+          <t>111858</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154414</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113339</t>
+          <t>111858</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>154414</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51171</t>
+          <t>51550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>26783</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51171</t>
+          <t>51550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6041,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6056,12 +6056,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6076,12 +6076,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20206</t>
+          <t>20671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27709</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51890</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6169,12 +6169,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -6197,12 +6197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1187333</t>
+          <t>1185070</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1253580</t>
+          <t>1251541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1187333</t>
+          <t>1185070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1253580</t>
+          <t>1251541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -6275,12 +6275,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81091</t>
+          <t>79156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>119348</t>
+          <t>115784</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6290,12 +6290,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81091</t>
+          <t>79156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119348</t>
+          <t>115784</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -6353,12 +6353,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168241</t>
+          <t>169599</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>220485</t>
+          <t>221777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168241</t>
+          <t>169599</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220485</t>
+          <t>221777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6513,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>23711</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6563,12 +6563,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15208</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -6747,12 +6747,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367602</t>
+          <t>366795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>404362</t>
+          <t>402948</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6762,12 +6762,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>367602</t>
+          <t>366795</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>404362</t>
+          <t>402948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -6825,12 +6825,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33373</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6860,12 +6860,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14476</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33373</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6903,12 +6903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68353</t>
+          <t>67496</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>39222</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>68353</t>
+          <t>67496</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -7063,12 +7063,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7098,12 +7098,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54519</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>90622</t>
+          <t>88327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7113,12 +7113,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -7141,12 +7141,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24258</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72531</t>
+          <t>71644</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>110186</t>
+          <t>111082</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>72531</t>
+          <t>71644</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>110186</t>
+          <t>111082</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2024866</t>
+          <t>2026652</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2115419</t>
+          <t>2118621</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7312,12 +7312,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7332,12 +7332,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2024866</t>
+          <t>2026652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2115419</t>
+          <t>2118621</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125194</t>
+          <t>123619</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>170624</t>
+          <t>172780</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>125194</t>
+          <t>123619</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>170624</t>
+          <t>172780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>341696</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>414108</t>
+          <t>414003</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>341696</t>
+          <t>338639</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>414108</t>
+          <t>414003</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -7778,32 +7778,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45874</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7813,32 +7813,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18851</t>
+          <t>16371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45874</t>
+          <t>31634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -7856,7 +7856,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -7934,32 +7934,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49964</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7969,32 +7969,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>44159</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31953</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>49964</t>
+          <t>53577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -8012,32 +8012,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>272562</t>
+          <t>297817</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>255158</t>
+          <t>280280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>288937</t>
+          <t>311567</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8047,32 +8047,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>272562</t>
+          <t>297817</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>255158</t>
+          <t>280280</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>288937</t>
+          <t>311567</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -8090,32 +8090,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9768</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14572</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8168,32 +8168,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78055</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>66125</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91020</t>
+          <t>97356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8203,32 +8203,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78055</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66125</t>
+          <t>73182</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>91020</t>
+          <t>97356</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -8246,17 +8246,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>427350</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>427350</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427350</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,17 +8281,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>427350</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>427350</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>427350</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8328,32 +8328,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>75108</t>
+          <t>84245</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58810</t>
+          <t>67779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93376</t>
+          <t>101996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8363,32 +8363,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>75108</t>
+          <t>84245</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>58810</t>
+          <t>67779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93376</t>
+          <t>101996</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -8406,32 +8406,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8441,32 +8441,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9297</t>
+          <t>10544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -8484,32 +8484,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8519,32 +8519,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>22701</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>16637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -8562,32 +8562,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>818964</t>
+          <t>829925</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>751538</t>
+          <t>800565</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>878552</t>
+          <t>858044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8597,32 +8597,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>818964</t>
+          <t>829925</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>751538</t>
+          <t>800565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>878552</t>
+          <t>858044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -8640,32 +8640,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37350</t>
+          <t>41044</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53384</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8675,32 +8675,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37350</t>
+          <t>41044</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>53384</t>
+          <t>57410</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8718,32 +8718,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>211145</t>
+          <t>199250</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>170067</t>
+          <t>177194</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292118</t>
+          <t>225235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8753,32 +8753,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>211145</t>
+          <t>199250</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170067</t>
+          <t>177194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>292118</t>
+          <t>225235</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -8796,17 +8796,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1172175</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1172175</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1172175</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8831,17 +8831,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1172175</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1172175</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1172175</t>
+          <t>1187710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8878,32 +8878,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8913,32 +8913,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17931</t>
+          <t>19101</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11957</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9016,7 +9016,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -9034,32 +9034,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9069,32 +9069,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4983</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2447</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9463</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -9112,32 +9112,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>323898</t>
+          <t>360313</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>308396</t>
+          <t>343231</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>337461</t>
+          <t>375116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9147,32 +9147,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>323898</t>
+          <t>360313</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>308396</t>
+          <t>343231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>337461</t>
+          <t>375116</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,13%</t>
         </is>
       </c>
     </row>
@@ -9190,32 +9190,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9225,32 +9225,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>19360</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -9268,32 +9268,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>36534</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53724</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9303,32 +9303,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>40683</t>
+          <t>47610</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30615</t>
+          <t>36534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>53724</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -9346,17 +9346,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>445897</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>445897</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>445897</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9381,17 +9381,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>445897</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>445897</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>399999</t>
+          <t>445897</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,32 +9428,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>119680</t>
+          <t>126478</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98254</t>
+          <t>107190</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143633</t>
+          <t>146884</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9463,32 +9463,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>119680</t>
+          <t>126478</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>98254</t>
+          <t>107190</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143633</t>
+          <t>146884</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -9506,32 +9506,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9541,32 +9541,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>21546</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -9584,32 +9584,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>86837</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9619,32 +9619,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>65013</t>
+          <t>72158</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>53225</t>
+          <t>61091</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>78140</t>
+          <t>86837</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1415424</t>
+          <t>1488055</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1342872</t>
+          <t>1447565</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1479989</t>
+          <t>1522823</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1415424</t>
+          <t>1488055</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1342872</t>
+          <t>1447565</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1479989</t>
+          <t>1522823</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>72,7%</t>
         </is>
       </c>
     </row>
@@ -9740,32 +9740,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>81630</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9775,32 +9775,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>62870</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>81630</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -9818,32 +9818,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>329882</t>
+          <t>331870</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>287784</t>
+          <t>301068</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>419289</t>
+          <t>365084</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -9853,32 +9853,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>329882</t>
+          <t>331870</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>287784</t>
+          <t>301068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>419289</t>
+          <t>365084</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -9896,17 +9896,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1999524</t>
+          <t>2094773</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1999524</t>
+          <t>2094773</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1999524</t>
+          <t>2094773</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -9931,17 +9931,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1999524</t>
+          <t>2094773</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1999524</t>
+          <t>2094773</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1999524</t>
+          <t>2094773</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
